--- a/data.xlsx
+++ b/data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25531\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7140" tabRatio="902"/>
+    <workbookView windowWidth="19200" windowHeight="7140" tabRatio="902" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="防汛" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <t>项目名称</t>
   </si>
   <si>
-    <t>项目属性</t>
+    <t>蝶城</t>
   </si>
   <si>
     <t>项目主管</t>
